--- a/10. Equity/work/fundamentals_model/20260721_ファンダメンタルズの検討③/outputs/diagnostics/binscatter_regression_summary.xlsx
+++ b/10. Equity/work/fundamentals_model/20260721_ファンダメンタルズの検討③/outputs/diagnostics/binscatter_regression_summary.xlsx
@@ -133,40 +133,40 @@
     <t>FA2001</t>
   </si>
   <si>
-    <t>0.0009601418377,0.006164316236</t>
-  </si>
-  <si>
-    <t>0.0008240936788,0.0003585050534</t>
-  </si>
-  <si>
-    <t>0.0009776321306,0.0035926294</t>
-  </si>
-  <si>
-    <t>0.0009518010478,0.004461334162</t>
-  </si>
-  <si>
-    <t>0.0004741265534,0.006164256449,0.0005103869203</t>
-  </si>
-  <si>
-    <t>0.00148154431,0.0003586169163,-0.0006913862454</t>
-  </si>
-  <si>
-    <t>0.0001963258242,0.003592441812,0.0008199729667</t>
-  </si>
-  <si>
-    <t>0.002012399628,0.004462040669,-0.001115352991</t>
-  </si>
-  <si>
-    <t>0.0002395136081,0.004912541309,0.005764962997</t>
-  </si>
-  <si>
-    <t>0.002277505401,0.002374431039,-0.004776091753</t>
-  </si>
-  <si>
-    <t>-0.0095659642,-0.004207352152,0.008836042735</t>
-  </si>
-  <si>
-    <t>0.007974518417,0.01076531409,-0.008073304266</t>
+    <t>0.0004581874863,0.004775642749</t>
+  </si>
+  <si>
+    <t>0.0005223255541,-7.087483433e-05</t>
+  </si>
+  <si>
+    <t>0.0004480556315,0.003729604462</t>
+  </si>
+  <si>
+    <t>0.0002467726579,0.003300271574</t>
+  </si>
+  <si>
+    <t>0.0003853095748,0.004775606647,7.660688855e-05</t>
+  </si>
+  <si>
+    <t>0.001125490964,-7.076819648e-05,-0.0006341264139</t>
+  </si>
+  <si>
+    <t>0.0004706760225,0.003729614819,-2.374676935e-05</t>
+  </si>
+  <si>
+    <t>0.0009870000926,0.003300766027,-0.0007781915982</t>
+  </si>
+  <si>
+    <t>0.000217742927,0.004300243075,0.004076735455</t>
+  </si>
+  <si>
+    <t>0.003341184072,0.002657276791,-0.003738270377</t>
+  </si>
+  <si>
+    <t>0.004165695051,0.006480697652,-0.0031162532</t>
+  </si>
+  <si>
+    <t>0.0008194973737,0.004296254868,-0.004585555202</t>
   </si>
   <si>
     <t>Bin</t>
@@ -760,49 +760,49 @@
         <v>20</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="G2">
-        <v>2787</v>
+        <v>4506</v>
       </c>
       <c r="H2">
-        <v>0.8927265402792505</v>
+        <v>0.9448658751846424</v>
       </c>
       <c r="I2">
-        <v>0.8210526315789473</v>
+        <v>0.932330827067669</v>
       </c>
       <c r="J2">
-        <v>0.02962092291650898</v>
+        <v>0.02335047800770525</v>
       </c>
       <c r="K2">
-        <v>0.7969606757189605</v>
+        <v>0.8927715220884402</v>
       </c>
       <c r="L2">
-        <v>0.7856807132589028</v>
+        <v>0.8868143844266869</v>
       </c>
       <c r="M2" t="s">
         <v>36</v>
       </c>
       <c r="N2">
-        <v>0.8054328024759352</v>
+        <v>0.8931273415313451</v>
       </c>
       <c r="O2">
-        <v>0.7825425439436923</v>
+        <v>0.8805540875938562</v>
       </c>
       <c r="P2" t="s">
         <v>40</v>
       </c>
       <c r="Q2">
-        <v>0.8352115621564964</v>
+        <v>0.9116084836081172</v>
       </c>
       <c r="R2">
-        <v>0.8158246871160841</v>
+        <v>0.9012094816796604</v>
       </c>
       <c r="S2" t="s">
         <v>44</v>
       </c>
       <c r="T2">
-        <v>0.7509510849417599</v>
+        <v>1.133412595462224</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -822,49 +822,49 @@
         <v>20</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="G3">
-        <v>2777</v>
+        <v>4503</v>
       </c>
       <c r="H3">
-        <v>0.09583336636208128</v>
+        <v>-0.02525876415230818</v>
       </c>
       <c r="I3">
-        <v>0.006015037593984962</v>
+        <v>-0.09924812030075188</v>
       </c>
       <c r="J3">
-        <v>0.00113759273432861</v>
+        <v>0.002241027729331908</v>
       </c>
       <c r="K3">
-        <v>0.00918403410828883</v>
+        <v>0.0006380051665021425</v>
       </c>
       <c r="L3">
-        <v>-0.04586129733013955</v>
+        <v>-0.054882105657581</v>
       </c>
       <c r="M3" t="s">
         <v>37</v>
       </c>
       <c r="N3">
-        <v>0.06205707230691659</v>
+        <v>0.07973897510781069</v>
       </c>
       <c r="O3">
-        <v>-0.04828915448050508</v>
+        <v>-0.02852702782068217</v>
       </c>
       <c r="P3" t="s">
         <v>41</v>
       </c>
       <c r="Q3">
-        <v>0.1489111507642636</v>
+        <v>0.1179882989672228</v>
       </c>
       <c r="R3">
-        <v>0.04878305085417711</v>
+        <v>0.01422221649277844</v>
       </c>
       <c r="S3" t="s">
         <v>45</v>
       </c>
       <c r="T3">
-        <v>0.1899274756109744</v>
+        <v>-0.5885703734513446</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -884,49 +884,49 @@
         <v>20</v>
       </c>
       <c r="F4">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="G4">
-        <v>2798</v>
+        <v>4529</v>
       </c>
       <c r="H4">
-        <v>0.6689144215732887</v>
+        <v>0.8376701483315063</v>
       </c>
       <c r="I4">
-        <v>0.6616541353383457</v>
+        <v>0.7789473684210525</v>
       </c>
       <c r="J4">
-        <v>0.01330285965140131</v>
+        <v>0.01780726686366326</v>
       </c>
       <c r="K4">
-        <v>0.4474465033887275</v>
+        <v>0.7016912774057277</v>
       </c>
       <c r="L4">
-        <v>0.4167490869103234</v>
+        <v>0.6851185705949348</v>
       </c>
       <c r="M4" t="s">
         <v>38</v>
       </c>
       <c r="N4">
-        <v>0.4837204168128851</v>
+        <v>0.7017355140338118</v>
       </c>
       <c r="O4">
-        <v>0.4229816423202833</v>
+        <v>0.6666455745083779</v>
       </c>
       <c r="P4" t="s">
         <v>42</v>
       </c>
       <c r="Q4">
-        <v>0.5259842623659243</v>
+        <v>0.7159003007972854</v>
       </c>
       <c r="R4">
-        <v>0.4702177049972096</v>
+        <v>0.6824768067734366</v>
       </c>
       <c r="S4" t="s">
         <v>46</v>
       </c>
       <c r="T4">
-        <v>-1.133634725563121</v>
+        <v>-1.133410412273488</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -946,49 +946,49 @@
         <v>20</v>
       </c>
       <c r="F5">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="G5">
-        <v>2776</v>
+        <v>4506</v>
       </c>
       <c r="H5">
-        <v>0.7538544352884835</v>
+        <v>0.7288324839486188</v>
       </c>
       <c r="I5">
-        <v>0.7293233082706766</v>
+        <v>0.6676691729323309</v>
       </c>
       <c r="J5">
-        <v>0.01778930085722137</v>
+        <v>0.01709649847040704</v>
       </c>
       <c r="K5">
-        <v>0.5682965096041184</v>
+        <v>0.5311967896587138</v>
       </c>
       <c r="L5">
-        <v>0.5443129823599027</v>
+        <v>0.5051521668619756</v>
       </c>
       <c r="M5" t="s">
         <v>39</v>
       </c>
       <c r="N5">
-        <v>0.6232523393699614</v>
+        <v>0.5769561866991553</v>
       </c>
       <c r="O5">
-        <v>0.5789290851781921</v>
+        <v>0.5271863263108206</v>
       </c>
       <c r="P5" t="s">
         <v>43</v>
       </c>
       <c r="Q5">
-        <v>0.6713799845180841</v>
+        <v>0.5875131419685615</v>
       </c>
       <c r="R5">
-        <v>0.632718806226094</v>
+        <v>0.538985276317804</v>
       </c>
       <c r="S5" t="s">
         <v>47</v>
       </c>
       <c r="T5">
-        <v>-0.7431814580116916</v>
+        <v>0.7505864848301731</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -1168,28 +1168,28 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>-2.025791418693221</v>
+        <v>-2.02477596512872</v>
       </c>
       <c r="C2">
-        <v>-0.0133858675153997</v>
+        <v>-0.01057720137745323</v>
       </c>
       <c r="D2">
-        <v>0.01700871960024573</v>
+        <v>0.01761963111872067</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F2">
-        <v>145</v>
+        <v>235</v>
       </c>
       <c r="G2">
         <v>5</v>
       </c>
       <c r="H2">
-        <v>0.003158439938126282</v>
+        <v>0.002570087343328229</v>
       </c>
       <c r="I2">
-        <v>0.006190542278727513</v>
+        <v>0.005037371192923328</v>
       </c>
       <c r="J2" t="s">
         <v>30</v>
@@ -1206,28 +1206,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>-1.425630263660492</v>
+        <v>-1.424345459993457</v>
       </c>
       <c r="C3">
-        <v>-0.006737020287888437</v>
+        <v>-0.007183574682255625</v>
       </c>
       <c r="D3">
-        <v>0.01632246858886125</v>
+        <v>0.01473949688954121</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F3">
-        <v>145</v>
+        <v>235</v>
       </c>
       <c r="G3">
         <v>5</v>
       </c>
       <c r="H3">
-        <v>0.003031006324492897</v>
+        <v>0.002149976588476172</v>
       </c>
       <c r="I3">
-        <v>0.005940772396006077</v>
+        <v>0.004213954113413297</v>
       </c>
       <c r="J3" t="s">
         <v>30</v>
@@ -1244,28 +1244,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>-1.133644687777892</v>
+        <v>-1.132827777571769</v>
       </c>
       <c r="C4">
-        <v>-0.001327008705139783</v>
+        <v>-0.003061476558535792</v>
       </c>
       <c r="D4">
-        <v>0.01949656877881134</v>
+        <v>0.01820925496190317</v>
       </c>
       <c r="E4">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F4">
-        <v>139</v>
+        <v>224</v>
       </c>
       <c r="G4">
-        <v>4.793103448275862</v>
+        <v>4.76595744680851</v>
       </c>
       <c r="H4">
-        <v>0.003620421932673523</v>
+        <v>0.002656092820201</v>
       </c>
       <c r="I4">
-        <v>0.007096026988040104</v>
+        <v>0.005205941927593959</v>
       </c>
       <c r="J4" t="s">
         <v>30</v>
@@ -1282,28 +1282,28 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>-0.9203792393379986</v>
+        <v>-0.9193750741304217</v>
       </c>
       <c r="C5">
-        <v>-0.003386043514537661</v>
+        <v>-0.00192090403357017</v>
       </c>
       <c r="D5">
-        <v>0.01879153683229454</v>
+        <v>0.01760818184495746</v>
       </c>
       <c r="E5">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F5">
-        <v>140</v>
+        <v>228</v>
       </c>
       <c r="G5">
-        <v>4.827586206896552</v>
+        <v>4.851063829787234</v>
       </c>
       <c r="H5">
-        <v>0.00348950078693946</v>
+        <v>0.002568417295108102</v>
       </c>
       <c r="I5">
-        <v>0.006839421542401342</v>
+        <v>0.005034097898411879</v>
       </c>
       <c r="J5" t="s">
         <v>30</v>
@@ -1320,28 +1320,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>-0.7437854991479698</v>
+        <v>-0.7432020891811625</v>
       </c>
       <c r="C6">
-        <v>-0.004667596347181948</v>
+        <v>-0.003344678304329013</v>
       </c>
       <c r="D6">
-        <v>0.021024677333365</v>
+        <v>0.01785096895187992</v>
       </c>
       <c r="E6">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F6">
-        <v>137</v>
+        <v>219</v>
       </c>
       <c r="G6">
-        <v>4.724137931034483</v>
+        <v>4.659574468085107</v>
       </c>
       <c r="H6">
-        <v>0.003904184567482611</v>
+        <v>0.002603831434395144</v>
       </c>
       <c r="I6">
-        <v>0.007652201752265918</v>
+        <v>0.005103509611414482</v>
       </c>
       <c r="J6" t="s">
         <v>30</v>
@@ -1358,28 +1358,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>-0.5896111609636139</v>
+        <v>-0.5900853620940348</v>
       </c>
       <c r="C7">
-        <v>-0.00318386672880769</v>
+        <v>-0.002722356754334929</v>
       </c>
       <c r="D7">
-        <v>0.01774605899177733</v>
+        <v>0.02102851702362098</v>
       </c>
       <c r="E7">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F7">
-        <v>137</v>
+        <v>221</v>
       </c>
       <c r="G7">
-        <v>4.724137931034483</v>
+        <v>4.702127659574468</v>
       </c>
       <c r="H7">
-        <v>0.003295360425788003</v>
+        <v>0.003067324456863806</v>
       </c>
       <c r="I7">
-        <v>0.006458906434544485</v>
+        <v>0.006011955935453059</v>
       </c>
       <c r="J7" t="s">
         <v>30</v>
@@ -1396,28 +1396,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>-0.4498741922857972</v>
+        <v>-0.4500549626227861</v>
       </c>
       <c r="C8">
-        <v>0.0006867090003026571</v>
+        <v>-0.000806079118007045</v>
       </c>
       <c r="D8">
-        <v>0.01780436483777317</v>
+        <v>0.01978770488962626</v>
       </c>
       <c r="E8">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F8">
-        <v>134</v>
+        <v>218</v>
       </c>
       <c r="G8">
-        <v>4.620689655172414</v>
+        <v>4.638297872340425</v>
       </c>
       <c r="H8">
-        <v>0.003306187549577901</v>
+        <v>0.002886333405488181</v>
       </c>
       <c r="I8">
-        <v>0.006480127597172686</v>
+        <v>0.005657213474756835</v>
       </c>
       <c r="J8" t="s">
         <v>30</v>
@@ -1434,28 +1434,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>-0.3156786832410948</v>
+        <v>-0.3146349210834956</v>
       </c>
       <c r="C9">
-        <v>-0.00238111777104349</v>
+        <v>-8.246682510722543E-05</v>
       </c>
       <c r="D9">
-        <v>0.01901722972451044</v>
+        <v>0.01598728495695189</v>
       </c>
       <c r="E9">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F9">
-        <v>143</v>
+        <v>234</v>
       </c>
       <c r="G9">
-        <v>4.931034482758621</v>
+        <v>4.978723404255319</v>
       </c>
       <c r="H9">
-        <v>0.00353141090488365</v>
+        <v>0.002331985184320204</v>
       </c>
       <c r="I9">
-        <v>0.006921565373571954</v>
+        <v>0.004570690961267601</v>
       </c>
       <c r="J9" t="s">
         <v>30</v>
@@ -1472,28 +1472,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>-0.1864865496957234</v>
+        <v>-0.1858830811039824</v>
       </c>
       <c r="C10">
-        <v>-0.0009100496224693504</v>
+        <v>-0.0019820780165689</v>
       </c>
       <c r="D10">
-        <v>0.01508805258315675</v>
+        <v>0.01754706157874004</v>
       </c>
       <c r="E10">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F10">
-        <v>135</v>
+        <v>214</v>
       </c>
       <c r="G10">
-        <v>4.655172413793103</v>
+        <v>4.553191489361702</v>
       </c>
       <c r="H10">
-        <v>0.002801781026862434</v>
+        <v>0.002559501987995949</v>
       </c>
       <c r="I10">
-        <v>0.005491490812650371</v>
+        <v>0.00501662389647206</v>
       </c>
       <c r="J10" t="s">
         <v>30</v>
@@ -1510,28 +1510,28 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>-0.05945655017178466</v>
+        <v>-0.05992226296082622</v>
       </c>
       <c r="C11">
-        <v>-4.580461166132808E-05</v>
+        <v>0.002525598436084952</v>
       </c>
       <c r="D11">
-        <v>0.01721158087906664</v>
+        <v>0.01624492216056018</v>
       </c>
       <c r="E11">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F11">
-        <v>145</v>
+        <v>235</v>
       </c>
       <c r="G11">
         <v>5</v>
       </c>
       <c r="H11">
-        <v>0.00319611033189996</v>
+        <v>0.00236956543283407</v>
       </c>
       <c r="I11">
-        <v>0.006264376250523921</v>
+        <v>0.004644348248354777</v>
       </c>
       <c r="J11" t="s">
         <v>30</v>
@@ -1548,28 +1548,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.06532254272642979</v>
+        <v>0.06548059083900135</v>
       </c>
       <c r="C12">
-        <v>0.00500089463857139</v>
+        <v>-0.0004891342475383728</v>
       </c>
       <c r="D12">
-        <v>0.01898907840385878</v>
+        <v>0.016251369327314</v>
       </c>
       <c r="E12">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F12">
-        <v>132</v>
+        <v>215</v>
       </c>
       <c r="G12">
-        <v>4.551724137931035</v>
+        <v>4.574468085106383</v>
       </c>
       <c r="H12">
-        <v>0.003526183335875109</v>
+        <v>0.002370505848757802</v>
       </c>
       <c r="I12">
-        <v>0.006911319338315213</v>
+        <v>0.004646191463565291</v>
       </c>
       <c r="J12" t="s">
         <v>30</v>
@@ -1586,28 +1586,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.1892492811435956</v>
+        <v>0.1893078863479334</v>
       </c>
       <c r="C13">
-        <v>-0.001298255071567615</v>
+        <v>0.002978182894501901</v>
       </c>
       <c r="D13">
-        <v>0.01983519653404246</v>
+        <v>0.01565774796479612</v>
       </c>
       <c r="E13">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F13">
-        <v>141</v>
+        <v>226</v>
       </c>
       <c r="G13">
-        <v>4.862068965517241</v>
+        <v>4.808510638297872</v>
       </c>
       <c r="H13">
-        <v>0.003683303528197301</v>
+        <v>0.002283917273761162</v>
       </c>
       <c r="I13">
-        <v>0.00721927491526671</v>
+        <v>0.004476477856571876</v>
       </c>
       <c r="J13" t="s">
         <v>30</v>
@@ -1624,28 +1624,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.3184981867060527</v>
+        <v>0.3181304441756069</v>
       </c>
       <c r="C14">
-        <v>0.002456901965867653</v>
+        <v>0.0004920195142182004</v>
       </c>
       <c r="D14">
-        <v>0.01622094734064801</v>
+        <v>0.01829298934066528</v>
       </c>
       <c r="E14">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F14">
-        <v>137</v>
+        <v>222</v>
       </c>
       <c r="G14">
-        <v>4.724137931034483</v>
+        <v>4.723404255319149</v>
       </c>
       <c r="H14">
-        <v>0.003012154301973782</v>
+        <v>0.002668306734647216</v>
       </c>
       <c r="I14">
-        <v>0.005903822431868613</v>
+        <v>0.005229881199908544</v>
       </c>
       <c r="J14" t="s">
         <v>30</v>
@@ -1662,28 +1662,28 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>0.4498741922857972</v>
+        <v>0.4500549626227861</v>
       </c>
       <c r="C15">
-        <v>0.001920065034939654</v>
+        <v>0.001187673326806003</v>
       </c>
       <c r="D15">
-        <v>0.01792547396968566</v>
+        <v>0.01472282942330843</v>
       </c>
       <c r="E15">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F15">
-        <v>134</v>
+        <v>218</v>
       </c>
       <c r="G15">
-        <v>4.620689655172414</v>
+        <v>4.638297872340425</v>
       </c>
       <c r="H15">
-        <v>0.00332867695078472</v>
+        <v>0.002147545388655836</v>
       </c>
       <c r="I15">
-        <v>0.006524206823538051</v>
+        <v>0.004209188961765438</v>
       </c>
       <c r="J15" t="s">
         <v>30</v>
@@ -1700,28 +1700,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>0.5928962960303011</v>
+        <v>0.5930981538604708</v>
       </c>
       <c r="C16">
-        <v>0.003552999460072349</v>
+        <v>0.001939257961735908</v>
       </c>
       <c r="D16">
-        <v>0.0173518813621987</v>
+        <v>0.01505719419887287</v>
       </c>
       <c r="E16">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F16">
-        <v>143</v>
+        <v>230</v>
       </c>
       <c r="G16">
-        <v>4.931034482758621</v>
+        <v>4.893617021276595</v>
       </c>
       <c r="H16">
-        <v>0.003222163477561571</v>
+        <v>0.002196317503800738</v>
       </c>
       <c r="I16">
-        <v>0.006315440416020679</v>
+        <v>0.004304782307449447</v>
       </c>
       <c r="J16" t="s">
         <v>30</v>
@@ -1738,28 +1738,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0.7509510849417599</v>
+        <v>0.7509501881253008</v>
       </c>
       <c r="C17">
-        <v>-0.004054375981377313</v>
+        <v>0.005937758013468308</v>
       </c>
       <c r="D17">
-        <v>0.02187525231985598</v>
+        <v>0.01737506451865616</v>
       </c>
       <c r="E17">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F17">
-        <v>137</v>
+        <v>222</v>
       </c>
       <c r="G17">
-        <v>4.724137931034483</v>
+        <v>4.723404255319149</v>
       </c>
       <c r="H17">
-        <v>0.004062132377243994</v>
+        <v>0.00253441363828915</v>
       </c>
       <c r="I17">
-        <v>0.007961779459398228</v>
+        <v>0.004967450731046733</v>
       </c>
       <c r="J17" t="s">
         <v>30</v>
@@ -1776,28 +1776,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0.9243914354214833</v>
+        <v>0.9243500718574867</v>
       </c>
       <c r="C18">
-        <v>0.009546970266561483</v>
+        <v>0.004140601719142297</v>
       </c>
       <c r="D18">
-        <v>0.01566621732479968</v>
+        <v>0.01563099411813073</v>
       </c>
       <c r="E18">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F18">
-        <v>134</v>
+        <v>216</v>
       </c>
       <c r="G18">
-        <v>4.620689655172414</v>
+        <v>4.595744680851064</v>
       </c>
       <c r="H18">
-        <v>0.002909143524083865</v>
+        <v>0.002280014824144778</v>
       </c>
       <c r="I18">
-        <v>0.005701921307204375</v>
+        <v>0.004468829055323765</v>
       </c>
       <c r="J18" t="s">
         <v>30</v>
@@ -1814,28 +1814,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>1.133644687777892</v>
+        <v>1.133412595462224</v>
       </c>
       <c r="C19">
-        <v>0.009618041543186436</v>
+        <v>0.002621342355961931</v>
       </c>
       <c r="D19">
-        <v>0.01060592442613273</v>
+        <v>0.01658442396237609</v>
       </c>
       <c r="E19">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F19">
-        <v>139</v>
+        <v>225</v>
       </c>
       <c r="G19">
-        <v>4.793103448275862</v>
+        <v>4.787234042553192</v>
       </c>
       <c r="H19">
-        <v>0.001969470722990972</v>
+        <v>0.002419086860269467</v>
       </c>
       <c r="I19">
-        <v>0.003860162617062306</v>
+        <v>0.004741410246128156</v>
       </c>
       <c r="J19" t="s">
         <v>30</v>
@@ -1852,28 +1852,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>1.425630263660492</v>
+        <v>1.425087800870378</v>
       </c>
       <c r="C20">
-        <v>0.01172193008883598</v>
+        <v>0.006879069414185045</v>
       </c>
       <c r="D20">
-        <v>0.01816345742179269</v>
+        <v>0.0183267790675881</v>
       </c>
       <c r="E20">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F20">
-        <v>145</v>
+        <v>234</v>
       </c>
       <c r="G20">
-        <v>5</v>
+        <v>4.978723404255319</v>
       </c>
       <c r="H20">
-        <v>0.003372869368404276</v>
+        <v>0.00267323547287753</v>
       </c>
       <c r="I20">
-        <v>0.00661082396207238</v>
+        <v>0.00523954152683996</v>
       </c>
       <c r="J20" t="s">
         <v>30</v>
@@ -1890,28 +1890,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>2.025791418693221</v>
+        <v>2.02477596512872</v>
       </c>
       <c r="C21">
-        <v>0.01623505540110928</v>
+        <v>0.01277327663025202</v>
       </c>
       <c r="D21">
-        <v>0.01909703210658743</v>
+        <v>0.01795462867567121</v>
       </c>
       <c r="E21">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F21">
-        <v>145</v>
+        <v>235</v>
       </c>
       <c r="G21">
         <v>5</v>
       </c>
       <c r="H21">
-        <v>0.00354622983521077</v>
+        <v>0.002618951759124636</v>
       </c>
       <c r="I21">
-        <v>0.006950610477013109</v>
+        <v>0.005133145447884286</v>
       </c>
       <c r="J21" t="s">
         <v>30</v>
@@ -1928,28 +1928,28 @@
         <v>1</v>
       </c>
       <c r="B22">
-        <v>-2.024282873479232</v>
+        <v>-2.024489290720134</v>
       </c>
       <c r="C22">
-        <v>-0.001160457377967469</v>
+        <v>-0.00315512758452979</v>
       </c>
       <c r="D22">
-        <v>0.01811357306623079</v>
+        <v>0.01875922282636746</v>
       </c>
       <c r="E22">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F22">
-        <v>145</v>
+        <v>235</v>
       </c>
       <c r="G22">
         <v>5</v>
       </c>
       <c r="H22">
-        <v>0.003363606076128465</v>
+        <v>0.002736313878075199</v>
       </c>
       <c r="I22">
-        <v>0.006592667909211791</v>
+        <v>0.00536317520102739</v>
       </c>
       <c r="J22" t="s">
         <v>30</v>
@@ -1966,28 +1966,28 @@
         <v>2</v>
       </c>
       <c r="B23">
-        <v>-1.423722177103146</v>
+        <v>-1.424726584382053</v>
       </c>
       <c r="C23">
-        <v>0.001590958053196365</v>
+        <v>0.002397414761261125</v>
       </c>
       <c r="D23">
-        <v>0.01638767010144455</v>
+        <v>0.01419095353957281</v>
       </c>
       <c r="E23">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F23">
-        <v>145</v>
+        <v>234</v>
       </c>
       <c r="G23">
-        <v>5</v>
+        <v>4.978723404255319</v>
       </c>
       <c r="H23">
-        <v>0.003043113941421707</v>
+        <v>0.002069963317396805</v>
       </c>
       <c r="I23">
-        <v>0.005964503325186546</v>
+        <v>0.004057128102097738</v>
       </c>
       <c r="J23" t="s">
         <v>30</v>
@@ -2004,28 +2004,28 @@
         <v>3</v>
       </c>
       <c r="B24">
-        <v>-1.133956954224986</v>
+        <v>-1.134029599480381</v>
       </c>
       <c r="C24">
-        <v>0.001553579210605383</v>
+        <v>0.0006538957424468805</v>
       </c>
       <c r="D24">
-        <v>0.02002878048201625</v>
+        <v>0.01458165345908874</v>
       </c>
       <c r="E24">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F24">
-        <v>136</v>
+        <v>223</v>
       </c>
       <c r="G24">
-        <v>4.689655172413793</v>
+        <v>4.74468085106383</v>
       </c>
       <c r="H24">
-        <v>0.003719251164881943</v>
+        <v>0.002126952757835223</v>
       </c>
       <c r="I24">
-        <v>0.007289732283168609</v>
+        <v>0.004168827405357038</v>
       </c>
       <c r="J24" t="s">
         <v>30</v>
@@ -2042,28 +2042,28 @@
         <v>4</v>
       </c>
       <c r="B25">
-        <v>-0.9207825596587728</v>
+        <v>-0.9202498739857184</v>
       </c>
       <c r="C25">
-        <v>-0.002138382717909975</v>
+        <v>-0.002280850006411986</v>
       </c>
       <c r="D25">
-        <v>0.01588002041795491</v>
+        <v>0.02198127574690891</v>
       </c>
       <c r="E25">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F25">
-        <v>142</v>
+        <v>229</v>
       </c>
       <c r="G25">
-        <v>4.896551724137931</v>
+        <v>4.872340425531915</v>
       </c>
       <c r="H25">
-        <v>0.002948845761770625</v>
+        <v>0.003206298599935744</v>
       </c>
       <c r="I25">
-        <v>0.005779737693070425</v>
+        <v>0.006284345255874057</v>
       </c>
       <c r="J25" t="s">
         <v>30</v>
@@ -2080,28 +2080,28 @@
         <v>5</v>
       </c>
       <c r="B26">
-        <v>-0.7422757667459351</v>
+        <v>-0.7423635941164473</v>
       </c>
       <c r="C26">
-        <v>-0.002480144428444959</v>
+        <v>0.002036611545163944</v>
       </c>
       <c r="D26">
-        <v>0.01486391895498873</v>
+        <v>0.01953347136598272</v>
       </c>
       <c r="E26">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F26">
-        <v>137</v>
+        <v>222</v>
       </c>
       <c r="G26">
-        <v>4.724137931034483</v>
+        <v>4.723404255319149</v>
       </c>
       <c r="H26">
-        <v>0.002760160456982924</v>
+        <v>0.002849249634723436</v>
       </c>
       <c r="I26">
-        <v>0.00540991449568653</v>
+        <v>0.005584529284057934</v>
       </c>
       <c r="J26" t="s">
         <v>30</v>
@@ -2118,28 +2118,28 @@
         <v>6</v>
       </c>
       <c r="B27">
-        <v>-0.5888022007636449</v>
+        <v>-0.5885703734513446</v>
       </c>
       <c r="C27">
-        <v>-0.002411028991054281</v>
+        <v>0.005352606590644927</v>
       </c>
       <c r="D27">
-        <v>0.02086793977215958</v>
+        <v>0.01428113139085381</v>
       </c>
       <c r="E27">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F27">
-        <v>135</v>
+        <v>220</v>
       </c>
       <c r="G27">
-        <v>4.655172413793103</v>
+        <v>4.680851063829787</v>
       </c>
       <c r="H27">
-        <v>0.003875079133049525</v>
+        <v>0.002083117108907207</v>
       </c>
       <c r="I27">
-        <v>0.007595155100777069</v>
+        <v>0.004082909533458125</v>
       </c>
       <c r="J27" t="s">
         <v>30</v>
@@ -2156,28 +2156,28 @@
         <v>7</v>
       </c>
       <c r="B28">
-        <v>-0.4496306251900575</v>
+        <v>-0.4494540509583221</v>
       </c>
       <c r="C28">
-        <v>-0.000319901770983975</v>
+        <v>-0.0001318965380872974</v>
       </c>
       <c r="D28">
-        <v>0.0245793626818266</v>
+        <v>0.01862749945069776</v>
       </c>
       <c r="E28">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F28">
-        <v>134</v>
+        <v>216</v>
       </c>
       <c r="G28">
-        <v>4.620689655172414</v>
+        <v>4.595744680851064</v>
       </c>
       <c r="H28">
-        <v>0.004564273065378198</v>
+        <v>0.002717100049003064</v>
       </c>
       <c r="I28">
-        <v>0.008945975208141268</v>
+        <v>0.005325516096046005</v>
       </c>
       <c r="J28" t="s">
         <v>30</v>
@@ -2194,28 +2194,28 @@
         <v>8</v>
       </c>
       <c r="B29">
-        <v>-0.3154136507423402</v>
+        <v>-0.3156974392021557</v>
       </c>
       <c r="C29">
-        <v>0.001372967664377792</v>
+        <v>-0.0002021416481040852</v>
       </c>
       <c r="D29">
-        <v>0.01674673744502203</v>
+        <v>0.0171545190599159</v>
       </c>
       <c r="E29">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F29">
-        <v>142</v>
+        <v>230</v>
       </c>
       <c r="G29">
-        <v>4.896551724137931</v>
+        <v>4.893617021276595</v>
       </c>
       <c r="H29">
-        <v>0.003109791073215664</v>
+        <v>0.002502243776825103</v>
       </c>
       <c r="I29">
-        <v>0.006095190503502702</v>
+        <v>0.004904397802577201</v>
       </c>
       <c r="J29" t="s">
         <v>30</v>
@@ -2232,28 +2232,28 @@
         <v>9</v>
       </c>
       <c r="B30">
-        <v>-0.1871647441631022</v>
+        <v>-0.1871315025561547</v>
       </c>
       <c r="C30">
-        <v>-0.002353839297644193</v>
+        <v>0.005185080380382312</v>
       </c>
       <c r="D30">
-        <v>0.01582675268693036</v>
+        <v>0.01668216779538006</v>
       </c>
       <c r="E30">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F30">
-        <v>133</v>
+        <v>217</v>
       </c>
       <c r="G30">
-        <v>4.586206896551724</v>
+        <v>4.617021276595745</v>
       </c>
       <c r="H30">
-        <v>0.002938954192444098</v>
+        <v>0.002433344263639562</v>
       </c>
       <c r="I30">
-        <v>0.005760350217190432</v>
+        <v>0.004769354756733542</v>
       </c>
       <c r="J30" t="s">
         <v>30</v>
@@ -2270,28 +2270,28 @@
         <v>10</v>
       </c>
       <c r="B31">
-        <v>-0.06058272791499028</v>
+        <v>-0.06049094092378913</v>
       </c>
       <c r="C31">
-        <v>0.003573538374611571</v>
+        <v>0.001341531351652484</v>
       </c>
       <c r="D31">
-        <v>0.0186273279125237</v>
+        <v>0.0172894037013781</v>
       </c>
       <c r="E31">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F31">
-        <v>145</v>
+        <v>234</v>
       </c>
       <c r="G31">
-        <v>5</v>
+        <v>4.978723404255319</v>
       </c>
       <c r="H31">
-        <v>0.003459007956050927</v>
+        <v>0.002521918723905184</v>
       </c>
       <c r="I31">
-        <v>0.006779655593859817</v>
+        <v>0.00494296069885416</v>
       </c>
       <c r="J31" t="s">
         <v>30</v>
@@ -2308,28 +2308,28 @@
         <v>11</v>
       </c>
       <c r="B32">
-        <v>0.06555704476136102</v>
+        <v>0.06522940926532786</v>
       </c>
       <c r="C32">
-        <v>0.003417880674719828</v>
+        <v>-0.0001360046991387833</v>
       </c>
       <c r="D32">
-        <v>0.01984055502009761</v>
+        <v>0.01934574313597127</v>
       </c>
       <c r="E32">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F32">
-        <v>134</v>
+        <v>217</v>
       </c>
       <c r="G32">
-        <v>4.620689655172414</v>
+        <v>4.617021276595745</v>
       </c>
       <c r="H32">
-        <v>0.00368429857407743</v>
+        <v>0.002821866658048901</v>
       </c>
       <c r="I32">
-        <v>0.007221225205191762</v>
+        <v>0.005530858649775846</v>
       </c>
       <c r="J32" t="s">
         <v>30</v>
@@ -2346,28 +2346,28 @@
         <v>12</v>
       </c>
       <c r="B33">
-        <v>0.1899274756109744</v>
+        <v>0.1899726093642502</v>
       </c>
       <c r="C33">
-        <v>0.009176935635419749</v>
+        <v>-0.003026852398992092</v>
       </c>
       <c r="D33">
-        <v>0.01690515072484417</v>
+        <v>0.02371428317112075</v>
       </c>
       <c r="E33">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F33">
-        <v>139</v>
+        <v>227</v>
       </c>
       <c r="G33">
-        <v>4.793103448275862</v>
+        <v>4.829787234042553</v>
       </c>
       <c r="H33">
-        <v>0.003139207680783972</v>
+        <v>0.003459083713134191</v>
       </c>
       <c r="I33">
-        <v>0.006152847054336585</v>
+        <v>0.006779804077743015</v>
       </c>
       <c r="J33" t="s">
         <v>30</v>
@@ -2384,28 +2384,28 @@
         <v>13</v>
       </c>
       <c r="B34">
-        <v>0.3182331542072981</v>
+        <v>0.3185969285810131</v>
       </c>
       <c r="C34">
-        <v>0.006193691755012344</v>
+        <v>-0.00266633986108743</v>
       </c>
       <c r="D34">
-        <v>0.01617843233624214</v>
+        <v>0.01778668573717245</v>
       </c>
       <c r="E34">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F34">
-        <v>136</v>
+        <v>220</v>
       </c>
       <c r="G34">
-        <v>4.689655172413793</v>
+        <v>4.680851063829787</v>
       </c>
       <c r="H34">
-        <v>0.003004259463853036</v>
+        <v>0.002594454763828382</v>
       </c>
       <c r="I34">
-        <v>0.00588834854915195</v>
+        <v>0.005085131337103628</v>
       </c>
       <c r="J34" t="s">
         <v>30</v>
@@ -2422,28 +2422,28 @@
         <v>14</v>
       </c>
       <c r="B35">
-        <v>0.4496306251900575</v>
+        <v>0.4494540509583221</v>
       </c>
       <c r="C35">
-        <v>-0.003129787406007412</v>
+        <v>0.00204966825307344</v>
       </c>
       <c r="D35">
-        <v>0.01744538276521116</v>
+        <v>0.02153610894538796</v>
       </c>
       <c r="E35">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F35">
-        <v>134</v>
+        <v>216</v>
       </c>
       <c r="G35">
-        <v>4.620689655172414</v>
+        <v>4.595744680851064</v>
       </c>
       <c r="H35">
-        <v>0.003239526252213998</v>
+        <v>0.003141364348216746</v>
       </c>
       <c r="I35">
-        <v>0.006349471454339436</v>
+        <v>0.006157074122504822</v>
       </c>
       <c r="J35" t="s">
         <v>30</v>
@@ -2460,28 +2460,28 @@
         <v>15</v>
       </c>
       <c r="B36">
-        <v>0.5921097869058218</v>
+        <v>0.5916247235915594</v>
       </c>
       <c r="C36">
-        <v>0.006597141321750026</v>
+        <v>0.004527534818205693</v>
       </c>
       <c r="D36">
-        <v>0.02084246231820708</v>
+        <v>0.01769393513123165</v>
       </c>
       <c r="E36">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F36">
-        <v>141</v>
+        <v>229</v>
       </c>
       <c r="G36">
-        <v>4.862068965517241</v>
+        <v>4.872340425531915</v>
       </c>
       <c r="H36">
-        <v>0.003870348088621924</v>
+        <v>0.002580925697481403</v>
       </c>
       <c r="I36">
-        <v>0.007585882253698972</v>
+        <v>0.00505861436706355</v>
       </c>
       <c r="J36" t="s">
         <v>30</v>
@@ -2498,28 +2498,28 @@
         <v>16</v>
       </c>
       <c r="B37">
-        <v>0.7494669845933453</v>
+        <v>0.7493874220635298</v>
       </c>
       <c r="C37">
-        <v>-0.001311781841589996</v>
+        <v>-0.003663324651926092</v>
       </c>
       <c r="D37">
-        <v>0.02238286420309465</v>
+        <v>0.0125041453885301</v>
       </c>
       <c r="E37">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F37">
-        <v>137</v>
+        <v>223</v>
       </c>
       <c r="G37">
-        <v>4.724137931034483</v>
+        <v>4.74468085106383</v>
       </c>
       <c r="H37">
-        <v>0.004156393537564689</v>
+        <v>0.00182391706078638</v>
       </c>
       <c r="I37">
-        <v>0.008146531333626791</v>
+        <v>0.003574877439141305</v>
       </c>
       <c r="J37" t="s">
         <v>30</v>
@@ -2536,28 +2536,28 @@
         <v>17</v>
       </c>
       <c r="B38">
-        <v>0.9247947557422573</v>
+        <v>0.9243758912346919</v>
       </c>
       <c r="C38">
-        <v>-0.003517430669899278</v>
+        <v>0.004011607496437428</v>
       </c>
       <c r="D38">
-        <v>0.02184578399218136</v>
+        <v>0.01796151368914243</v>
       </c>
       <c r="E38">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F38">
-        <v>136</v>
+        <v>219</v>
       </c>
       <c r="G38">
-        <v>4.689655172413793</v>
+        <v>4.659574468085107</v>
       </c>
       <c r="H38">
-        <v>0.004056660246170944</v>
+        <v>0.002619956041556077</v>
       </c>
       <c r="I38">
-        <v>0.00795105408249505</v>
+        <v>0.005135113841449911</v>
       </c>
       <c r="J38" t="s">
         <v>30</v>
@@ -2574,28 +2574,28 @@
         <v>18</v>
       </c>
       <c r="B39">
-        <v>1.133956954224986</v>
+        <v>1.134029599480381</v>
       </c>
       <c r="C39">
-        <v>0.005005538514594969</v>
+        <v>7.363964882032302E-05</v>
       </c>
       <c r="D39">
-        <v>0.02008188447489563</v>
+        <v>0.01588801652936157</v>
       </c>
       <c r="E39">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F39">
-        <v>136</v>
+        <v>223</v>
       </c>
       <c r="G39">
-        <v>4.689655172413793</v>
+        <v>4.74468085106383</v>
       </c>
       <c r="H39">
-        <v>0.003729112328798231</v>
+        <v>0.002317505395973733</v>
       </c>
       <c r="I39">
-        <v>0.007309060164444534</v>
+        <v>0.004542310576108517</v>
       </c>
       <c r="J39" t="s">
         <v>30</v>
@@ -2612,28 +2612,28 @@
         <v>19</v>
       </c>
       <c r="B40">
-        <v>1.423722177103146</v>
+        <v>1.424726584382053</v>
       </c>
       <c r="C40">
-        <v>-0.003145751639671288</v>
+        <v>-0.001008191684098978</v>
       </c>
       <c r="D40">
-        <v>0.01472566396134406</v>
+        <v>0.01778441335760137</v>
       </c>
       <c r="E40">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F40">
-        <v>145</v>
+        <v>234</v>
       </c>
       <c r="G40">
-        <v>5</v>
+        <v>4.978723404255319</v>
       </c>
       <c r="H40">
-        <v>0.002734487149183411</v>
+        <v>0.002594123303201566</v>
       </c>
       <c r="I40">
-        <v>0.005359594812399486</v>
+        <v>0.00508448167427507</v>
       </c>
       <c r="J40" t="s">
         <v>30</v>
@@ -2650,28 +2650,28 @@
         <v>20</v>
       </c>
       <c r="B41">
-        <v>2.024282873479232</v>
+        <v>2.024489290720135</v>
       </c>
       <c r="C41">
-        <v>-2.286464363885864E-05</v>
+        <v>-0.0009140998551978825</v>
       </c>
       <c r="D41">
-        <v>0.01520097951640643</v>
+        <v>0.01901998425885111</v>
       </c>
       <c r="E41">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F41">
-        <v>145</v>
+        <v>235</v>
       </c>
       <c r="G41">
         <v>5</v>
       </c>
       <c r="H41">
-        <v>0.00282275103192153</v>
+        <v>0.002774349842207406</v>
       </c>
       <c r="I41">
-        <v>0.005532592022566199</v>
+        <v>0.005437725690726516</v>
       </c>
       <c r="J41" t="s">
         <v>30</v>
@@ -2688,28 +2688,28 @@
         <v>1</v>
       </c>
       <c r="B42">
-        <v>-2.02750499996917</v>
+        <v>-2.026946552105255</v>
       </c>
       <c r="C42">
-        <v>-0.001052296950856285</v>
+        <v>-0.008819245549662784</v>
       </c>
       <c r="D42">
-        <v>0.01569678505796979</v>
+        <v>0.01924847726394493</v>
       </c>
       <c r="E42">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F42">
-        <v>145</v>
+        <v>235</v>
       </c>
       <c r="G42">
         <v>5</v>
       </c>
       <c r="H42">
-        <v>0.002914819809632195</v>
+        <v>0.002807678972452744</v>
       </c>
       <c r="I42">
-        <v>0.005713046826879103</v>
+        <v>0.005503050786007379</v>
       </c>
       <c r="J42" t="s">
         <v>30</v>
@@ -2726,28 +2726,28 @@
         <v>2</v>
       </c>
       <c r="B43">
-        <v>-1.427802343831763</v>
+        <v>-1.427093460132337</v>
       </c>
       <c r="C43">
-        <v>-0.003507768447938878</v>
+        <v>-0.005542551686886505</v>
       </c>
       <c r="D43">
-        <v>0.01452813942623189</v>
+        <v>0.01862994433211102</v>
       </c>
       <c r="E43">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F43">
-        <v>145</v>
+        <v>235</v>
       </c>
       <c r="G43">
         <v>5</v>
       </c>
       <c r="H43">
-        <v>0.002697807763837491</v>
+        <v>0.002717456671609623</v>
       </c>
       <c r="I43">
-        <v>0.005287703217121482</v>
+        <v>0.005326215076354861</v>
       </c>
       <c r="J43" t="s">
         <v>30</v>
@@ -2764,28 +2764,28 @@
         <v>3</v>
       </c>
       <c r="B44">
-        <v>-1.133634725563121</v>
+        <v>-1.133410412273488</v>
       </c>
       <c r="C44">
-        <v>-0.006421390063382822</v>
+        <v>-0.002396017970849836</v>
       </c>
       <c r="D44">
-        <v>0.01856908302489999</v>
+        <v>0.01535803653950633</v>
       </c>
       <c r="E44">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F44">
-        <v>142</v>
+        <v>229</v>
       </c>
       <c r="G44">
-        <v>4.896551724137931</v>
+        <v>4.872340425531915</v>
       </c>
       <c r="H44">
-        <v>0.003448192151946557</v>
+        <v>0.002240199869259445</v>
       </c>
       <c r="I44">
-        <v>0.006758456617815251</v>
+        <v>0.004390791743748512</v>
       </c>
       <c r="J44" t="s">
         <v>30</v>
@@ -2802,28 +2802,28 @@
         <v>4</v>
       </c>
       <c r="B45">
-        <v>-0.917629382574398</v>
+        <v>-0.9181790130536615</v>
       </c>
       <c r="C45">
-        <v>0.0006234585015337032</v>
+        <v>-0.003367078959054958</v>
       </c>
       <c r="D45">
-        <v>0.01683201400580792</v>
+        <v>0.02121931334360524</v>
       </c>
       <c r="E45">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F45">
-        <v>142</v>
+        <v>229</v>
       </c>
       <c r="G45">
-        <v>4.896551724137931</v>
+        <v>4.872340425531915</v>
       </c>
       <c r="H45">
-        <v>0.003125626533009375</v>
+        <v>0.003095154960456139</v>
       </c>
       <c r="I45">
-        <v>0.006126228004698375</v>
+        <v>0.006066503722494032</v>
       </c>
       <c r="J45" t="s">
         <v>30</v>
@@ -2840,28 +2840,28 @@
         <v>5</v>
       </c>
       <c r="B46">
-        <v>-0.7408503237441413</v>
+        <v>-0.7415697535564726</v>
       </c>
       <c r="C46">
-        <v>-0.009266980299272053</v>
+        <v>0.003066443715596209</v>
       </c>
       <c r="D46">
-        <v>0.02261918637425661</v>
+        <v>0.01798904041526404</v>
       </c>
       <c r="E46">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F46">
-        <v>137</v>
+        <v>222</v>
       </c>
       <c r="G46">
-        <v>4.724137931034483</v>
+        <v>4.723404255319149</v>
       </c>
       <c r="H46">
-        <v>0.004200277463057346</v>
+        <v>0.002623971227227771</v>
       </c>
       <c r="I46">
-        <v>0.008232543827592398</v>
+        <v>0.005142983605366432</v>
       </c>
       <c r="J46" t="s">
         <v>30</v>
@@ -2878,28 +2878,28 @@
         <v>6</v>
       </c>
       <c r="B47">
-        <v>-0.5885971725671687</v>
+        <v>-0.588674800154333</v>
       </c>
       <c r="C47">
-        <v>0.001686002674011377</v>
+        <v>-0.00110982102936028</v>
       </c>
       <c r="D47">
-        <v>0.01355143050876254</v>
+        <v>0.02012146021586943</v>
       </c>
       <c r="E47">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F47">
-        <v>135</v>
+        <v>220</v>
       </c>
       <c r="G47">
-        <v>4.655172413793103</v>
+        <v>4.680851063829787</v>
       </c>
       <c r="H47">
-        <v>0.002516437471107478</v>
+        <v>0.002935016623313018</v>
       </c>
       <c r="I47">
-        <v>0.004932217443370657</v>
+        <v>0.005752632581693516</v>
       </c>
       <c r="J47" t="s">
         <v>30</v>
@@ -2916,28 +2916,28 @@
         <v>7</v>
       </c>
       <c r="B48">
-        <v>-0.4489772497629538</v>
+        <v>-0.4488298913450061</v>
       </c>
       <c r="C48">
-        <v>-0.004948384502830644</v>
+        <v>-0.004523684521967699</v>
       </c>
       <c r="D48">
-        <v>0.02315435590162294</v>
+        <v>0.01592491731502802</v>
       </c>
       <c r="E48">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F48">
-        <v>137</v>
+        <v>221</v>
       </c>
       <c r="G48">
-        <v>4.724137931034483</v>
+        <v>4.702127659574468</v>
       </c>
       <c r="H48">
-        <v>0.004299655949423688</v>
+        <v>0.002322887928761237</v>
       </c>
       <c r="I48">
-        <v>0.008427325660870429</v>
+        <v>0.004552860340372024</v>
       </c>
       <c r="J48" t="s">
         <v>30</v>
@@ -2954,28 +2954,28 @@
         <v>8</v>
       </c>
       <c r="B49">
-        <v>-0.3143855272001715</v>
+        <v>-0.3141489660333444</v>
       </c>
       <c r="C49">
-        <v>0.0005596701005314453</v>
+        <v>0.0001879562191180929</v>
       </c>
       <c r="D49">
-        <v>0.01832823983970506</v>
+        <v>0.0171871795148471</v>
       </c>
       <c r="E49">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F49">
-        <v>142</v>
+        <v>231</v>
       </c>
       <c r="G49">
-        <v>4.896551724137931</v>
+        <v>4.914893617021277</v>
       </c>
       <c r="H49">
-        <v>0.003403468695224147</v>
+        <v>0.002507007793805959</v>
       </c>
       <c r="I49">
-        <v>0.006670798642639328</v>
+        <v>0.00491373527585968</v>
       </c>
       <c r="J49" t="s">
         <v>30</v>
@@ -2992,28 +2992,28 @@
         <v>9</v>
       </c>
       <c r="B50">
-        <v>-0.1852889852991867</v>
+        <v>-0.1846626452984159</v>
       </c>
       <c r="C50">
-        <v>-0.001635770858603202</v>
+        <v>-0.002022625503684644</v>
       </c>
       <c r="D50">
-        <v>0.01752320619941587</v>
+        <v>0.0210651863315299</v>
       </c>
       <c r="E50">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F50">
-        <v>137</v>
+        <v>222</v>
       </c>
       <c r="G50">
-        <v>4.724137931034483</v>
+        <v>4.723404255319149</v>
       </c>
       <c r="H50">
-        <v>0.003253977701146741</v>
+        <v>0.003072673225150173</v>
       </c>
       <c r="I50">
-        <v>0.006377796294247612</v>
+        <v>0.006022439521294339</v>
       </c>
       <c r="J50" t="s">
         <v>30</v>
@@ -3030,28 +3030,28 @@
         <v>10</v>
       </c>
       <c r="B51">
-        <v>-0.05785422654353659</v>
+        <v>-0.05709555518979421</v>
       </c>
       <c r="C51">
-        <v>-0.001879976996734364</v>
+        <v>0.00102817099896916</v>
       </c>
       <c r="D51">
-        <v>0.01629125876796813</v>
+        <v>0.01627264244928352</v>
       </c>
       <c r="E51">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F51">
-        <v>145</v>
+        <v>235</v>
       </c>
       <c r="G51">
         <v>5</v>
       </c>
       <c r="H51">
-        <v>0.003025210806247703</v>
+        <v>0.002373608852513018</v>
       </c>
       <c r="I51">
-        <v>0.005929413180245498</v>
+        <v>0.004652273350925515</v>
       </c>
       <c r="J51" t="s">
         <v>30</v>
@@ -3068,28 +3068,28 @@
         <v>11</v>
       </c>
       <c r="B52">
-        <v>0.06504971785289465</v>
+        <v>0.06513833519266349</v>
       </c>
       <c r="C52">
-        <v>0.005119208520492438</v>
+        <v>0.00357107876554181</v>
       </c>
       <c r="D52">
-        <v>0.01846005639142767</v>
+        <v>0.0145063703439641</v>
       </c>
       <c r="E52">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F52">
-        <v>129</v>
+        <v>206</v>
       </c>
       <c r="G52">
-        <v>4.448275862068965</v>
+        <v>4.382978723404255</v>
       </c>
       <c r="H52">
-        <v>0.003427946414373609</v>
+        <v>0.002115971586887633</v>
       </c>
       <c r="I52">
-        <v>0.006718774972172273</v>
+        <v>0.004147304310299761</v>
       </c>
       <c r="J52" t="s">
         <v>30</v>
@@ -3106,28 +3106,28 @@
         <v>12</v>
       </c>
       <c r="B53">
-        <v>0.1889726272296829</v>
+        <v>0.188087450542367</v>
       </c>
       <c r="C53">
-        <v>-0.003182287045004079</v>
+        <v>0.0006187898656405721</v>
       </c>
       <c r="D53">
-        <v>0.01330460124804554</v>
+        <v>0.01504028705919354</v>
       </c>
       <c r="E53">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F53">
-        <v>145</v>
+        <v>234</v>
       </c>
       <c r="G53">
-        <v>5</v>
+        <v>4.978723404255319</v>
       </c>
       <c r="H53">
-        <v>0.002470602428066642</v>
+        <v>0.002193851344015159</v>
       </c>
       <c r="I53">
-        <v>0.004842380759010619</v>
+        <v>0.004299948634269711</v>
       </c>
       <c r="J53" t="s">
         <v>30</v>
@@ -3144,28 +3144,28 @@
         <v>13</v>
       </c>
       <c r="B54">
-        <v>0.3181448651534488</v>
+        <v>0.3176444891254557</v>
       </c>
       <c r="C54">
-        <v>0.006176728310668943</v>
+        <v>0.002487113422279201</v>
       </c>
       <c r="D54">
-        <v>0.01941547969111193</v>
+        <v>0.0153406747967224</v>
       </c>
       <c r="E54">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F54">
-        <v>134</v>
+        <v>219</v>
       </c>
       <c r="G54">
-        <v>4.620689655172414</v>
+        <v>4.659574468085107</v>
       </c>
       <c r="H54">
-        <v>0.003605364067110713</v>
+        <v>0.002237667398795878</v>
       </c>
       <c r="I54">
-        <v>0.007066513571536998</v>
+        <v>0.004385828101639922</v>
       </c>
       <c r="J54" t="s">
         <v>30</v>
@@ -3182,28 +3182,28 @@
         <v>14</v>
       </c>
       <c r="B55">
-        <v>0.4489772497629538</v>
+        <v>0.448829891345006</v>
       </c>
       <c r="C55">
-        <v>0.004675025111438148</v>
+        <v>0.00337164856598051</v>
       </c>
       <c r="D55">
-        <v>0.01781281067272289</v>
+        <v>0.02022028103815903</v>
       </c>
       <c r="E55">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F55">
-        <v>137</v>
+        <v>221</v>
       </c>
       <c r="G55">
-        <v>4.724137931034483</v>
+        <v>4.702127659574468</v>
       </c>
       <c r="H55">
-        <v>0.003307755901755076</v>
+        <v>0.002949431121716106</v>
       </c>
       <c r="I55">
-        <v>0.006483201567439949</v>
+        <v>0.005780884998563568</v>
       </c>
       <c r="J55" t="s">
         <v>30</v>
@@ -3220,28 +3220,28 @@
         <v>15</v>
       </c>
       <c r="B56">
-        <v>0.5940649139864844</v>
+        <v>0.5937284429446655</v>
       </c>
       <c r="C56">
-        <v>0.006196624199920455</v>
+        <v>-0.002058653427028021</v>
       </c>
       <c r="D56">
-        <v>0.02266499881427813</v>
+        <v>0.01960978207285687</v>
       </c>
       <c r="E56">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F56">
-        <v>145</v>
+        <v>235</v>
       </c>
       <c r="G56">
         <v>5</v>
       </c>
       <c r="H56">
-        <v>0.004208784619599857</v>
+        <v>0.002860380695332833</v>
       </c>
       <c r="I56">
-        <v>0.008249217854415718</v>
+        <v>0.005606346162852353</v>
       </c>
       <c r="J56" t="s">
         <v>30</v>
@@ -3258,28 +3258,28 @@
         <v>16</v>
       </c>
       <c r="B57">
-        <v>0.751565553617433</v>
+        <v>0.7514987824156467</v>
       </c>
       <c r="C57">
-        <v>0.002163535660253698</v>
+        <v>-0.001741827730807984</v>
       </c>
       <c r="D57">
-        <v>0.01845967940381887</v>
+        <v>0.01551642575164761</v>
       </c>
       <c r="E57">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F57">
-        <v>135</v>
+        <v>219</v>
       </c>
       <c r="G57">
-        <v>4.655172413793103</v>
+        <v>4.659574468085107</v>
       </c>
       <c r="H57">
-        <v>0.003427876409532104</v>
+        <v>0.00226330331034179</v>
       </c>
       <c r="I57">
-        <v>0.006718637762682923</v>
+        <v>0.004436074488269909</v>
       </c>
       <c r="J57" t="s">
         <v>30</v>
@@ -3296,28 +3296,28 @@
         <v>17</v>
       </c>
       <c r="B58">
-        <v>0.9229789773523774</v>
+        <v>0.9231540107807265</v>
       </c>
       <c r="C58">
-        <v>0.004478985273676732</v>
+        <v>0.005279474042187228</v>
       </c>
       <c r="D58">
-        <v>0.01447877857050753</v>
+        <v>0.01791703092236939</v>
       </c>
       <c r="E58">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F58">
-        <v>134</v>
+        <v>217</v>
       </c>
       <c r="G58">
-        <v>4.620689655172414</v>
+        <v>4.617021276595745</v>
       </c>
       <c r="H58">
-        <v>0.002688641683041048</v>
+        <v>0.002613467563158924</v>
       </c>
       <c r="I58">
-        <v>0.005269737698760453</v>
+        <v>0.005122396423791492</v>
       </c>
       <c r="J58" t="s">
         <v>30</v>
@@ -3334,28 +3334,28 @@
         <v>18</v>
       </c>
       <c r="B59">
-        <v>1.133634725563121</v>
+        <v>1.133995230163943</v>
       </c>
       <c r="C59">
-        <v>0.009092406253892011</v>
+        <v>0.005609743400122739</v>
       </c>
       <c r="D59">
-        <v>0.01957168197813992</v>
+        <v>0.01827216867884008</v>
       </c>
       <c r="E59">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F59">
-        <v>142</v>
+        <v>230</v>
       </c>
       <c r="G59">
-        <v>4.896551724137931</v>
+        <v>4.893617021276595</v>
       </c>
       <c r="H59">
-        <v>0.003634370103624404</v>
+        <v>0.002665269728987104</v>
       </c>
       <c r="I59">
-        <v>0.007123365403103832</v>
+        <v>0.005223928668814723</v>
       </c>
       <c r="J59" t="s">
         <v>30</v>
@@ -3372,28 +3372,28 @@
         <v>19</v>
       </c>
       <c r="B60">
-        <v>1.427802343831763</v>
+        <v>1.427835801009258</v>
       </c>
       <c r="C60">
-        <v>-0.001444760398219773</v>
+        <v>0.006469369165146353</v>
       </c>
       <c r="D60">
-        <v>0.0190513300879814</v>
+        <v>0.01681510334730893</v>
       </c>
       <c r="E60">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F60">
-        <v>145</v>
+        <v>234</v>
       </c>
       <c r="G60">
-        <v>5</v>
+        <v>4.978723404255319</v>
       </c>
       <c r="H60">
-        <v>0.00353774318341035</v>
+        <v>0.002452734906791436</v>
       </c>
       <c r="I60">
-        <v>0.006933976639484286</v>
+        <v>0.004807360417311214</v>
       </c>
       <c r="J60" t="s">
         <v>30</v>
@@ -3410,28 +3410,28 @@
         <v>20</v>
       </c>
       <c r="B61">
-        <v>2.02750499996917</v>
+        <v>2.026946552105256</v>
       </c>
       <c r="C61">
-        <v>0.01225056270054503</v>
+        <v>0.008988021314000481</v>
       </c>
       <c r="D61">
-        <v>0.01945542026342864</v>
+        <v>0.02033470088746394</v>
       </c>
       <c r="E61">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F61">
-        <v>145</v>
+        <v>235</v>
       </c>
       <c r="G61">
         <v>5</v>
       </c>
       <c r="H61">
-        <v>0.003612780845194048</v>
+        <v>0.002966120972062157</v>
       </c>
       <c r="I61">
-        <v>0.007081050456580334</v>
+        <v>0.005813597105241828</v>
       </c>
       <c r="J61" t="s">
         <v>30</v>
@@ -3448,28 +3448,28 @@
         <v>1</v>
       </c>
       <c r="B62">
-        <v>-2.024128579368942</v>
+        <v>-2.0247849307354</v>
       </c>
       <c r="C62">
-        <v>-0.01116436064000334</v>
+        <v>-0.009558215665737505</v>
       </c>
       <c r="D62">
-        <v>0.01714936374079353</v>
+        <v>0.01621898045687597</v>
       </c>
       <c r="E62">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F62">
-        <v>145</v>
+        <v>235</v>
       </c>
       <c r="G62">
         <v>5</v>
       </c>
       <c r="H62">
-        <v>0.003184556899367925</v>
+        <v>0.002365781446446732</v>
       </c>
       <c r="I62">
-        <v>0.006241731522761134</v>
+        <v>0.004636931635035594</v>
       </c>
       <c r="J62" t="s">
         <v>30</v>
@@ -3486,28 +3486,28 @@
         <v>2</v>
       </c>
       <c r="B63">
-        <v>-1.423526733174129</v>
+        <v>-1.424357573410764</v>
       </c>
       <c r="C63">
-        <v>-0.01476264320685113</v>
+        <v>-0.00333590359526563</v>
       </c>
       <c r="D63">
-        <v>0.01616257068922254</v>
+        <v>0.01809152089201725</v>
       </c>
       <c r="E63">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F63">
-        <v>145</v>
+        <v>235</v>
       </c>
       <c r="G63">
         <v>5</v>
       </c>
       <c r="H63">
-        <v>0.003001314029945685</v>
+        <v>0.002638919541098078</v>
       </c>
       <c r="I63">
-        <v>0.005882575498693543</v>
+        <v>0.005172282300552234</v>
       </c>
       <c r="J63" t="s">
         <v>30</v>
@@ -3524,28 +3524,28 @@
         <v>3</v>
       </c>
       <c r="B64">
-        <v>-1.132062652005902</v>
+        <v>-1.13232568515586</v>
       </c>
       <c r="C64">
-        <v>-4.274201604682461E-05</v>
+        <v>-0.006868253876769112</v>
       </c>
       <c r="D64">
-        <v>0.02022335678435066</v>
+        <v>0.01584012641988032</v>
       </c>
       <c r="E64">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F64">
-        <v>138</v>
+        <v>225</v>
       </c>
       <c r="G64">
-        <v>4.758620689655173</v>
+        <v>4.787234042553192</v>
       </c>
       <c r="H64">
-        <v>0.003755383077145172</v>
+        <v>0.002310519905561418</v>
       </c>
       <c r="I64">
-        <v>0.007360550831204537</v>
+        <v>0.00452861901490038</v>
       </c>
       <c r="J64" t="s">
         <v>30</v>
@@ -3562,28 +3562,28 @@
         <v>4</v>
       </c>
       <c r="B65">
-        <v>-0.9197437956962432</v>
+        <v>-0.919767689463258</v>
       </c>
       <c r="C65">
-        <v>-0.001784906675519566</v>
+        <v>-0.001307289063997899</v>
       </c>
       <c r="D65">
-        <v>0.01996432995808648</v>
+        <v>0.01663912292370254</v>
       </c>
       <c r="E65">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F65">
-        <v>139</v>
+        <v>225</v>
       </c>
       <c r="G65">
-        <v>4.793103448275862</v>
+        <v>4.787234042553192</v>
       </c>
       <c r="H65">
-        <v>0.003707283003045118</v>
+        <v>0.002427065523798294</v>
       </c>
       <c r="I65">
-        <v>0.00726627468596843</v>
+        <v>0.004757048426644657</v>
       </c>
       <c r="J65" t="s">
         <v>30</v>
@@ -3600,28 +3600,28 @@
         <v>5</v>
       </c>
       <c r="B66">
-        <v>-0.7431814580116916</v>
+        <v>-0.7421577584305014</v>
       </c>
       <c r="C66">
-        <v>0.0001519040035455868</v>
+        <v>-6.405742504835464E-05</v>
       </c>
       <c r="D66">
-        <v>0.01554984105252624</v>
+        <v>0.01592097220515803</v>
       </c>
       <c r="E66">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F66">
-        <v>137</v>
+        <v>226</v>
       </c>
       <c r="G66">
-        <v>4.724137931034483</v>
+        <v>4.808510638297872</v>
       </c>
       <c r="H66">
-        <v>0.002887532992848264</v>
+        <v>0.002322312475343591</v>
       </c>
       <c r="I66">
-        <v>0.005659564665982598</v>
+        <v>0.004551732451673439</v>
       </c>
       <c r="J66" t="s">
         <v>30</v>
@@ -3638,28 +3638,28 @@
         <v>6</v>
       </c>
       <c r="B67">
-        <v>-0.5895211693050764</v>
+        <v>-0.588389441872972</v>
       </c>
       <c r="C67">
-        <v>0.004071566522706441</v>
+        <v>-0.0007620066745842298</v>
       </c>
       <c r="D67">
-        <v>0.02249420681620895</v>
+        <v>0.01637747946343757</v>
       </c>
       <c r="E67">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F67">
-        <v>135</v>
+        <v>216</v>
       </c>
       <c r="G67">
-        <v>4.655172413793103</v>
+        <v>4.595744680851064</v>
       </c>
       <c r="H67">
-        <v>0.004177069341760467</v>
+        <v>0.002388900902691264</v>
       </c>
       <c r="I67">
-        <v>0.008187055909850515</v>
+        <v>0.004682245769274876</v>
       </c>
       <c r="J67" t="s">
         <v>30</v>
@@ -3676,28 +3676,28 @@
         <v>7</v>
       </c>
       <c r="B68">
-        <v>-0.4502591638246705</v>
+        <v>-0.4506335788764816</v>
       </c>
       <c r="C68">
-        <v>-0.00215382814995321</v>
+        <v>-0.002756972035608495</v>
       </c>
       <c r="D68">
-        <v>0.02308913926591821</v>
+        <v>0.02005111257205514</v>
       </c>
       <c r="E68">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F68">
-        <v>134</v>
+        <v>216</v>
       </c>
       <c r="G68">
-        <v>4.620689655172414</v>
+        <v>4.595744680851064</v>
       </c>
       <c r="H68">
-        <v>0.004287545524201729</v>
+        <v>0.00292475536484615</v>
       </c>
       <c r="I68">
-        <v>0.008403589227435389</v>
+        <v>0.005732520515098453</v>
       </c>
       <c r="J68" t="s">
         <v>30</v>
@@ -3714,28 +3714,28 @@
         <v>8</v>
       </c>
       <c r="B69">
-        <v>-0.3155228714431795</v>
+        <v>-0.31635813692488</v>
       </c>
       <c r="C69">
-        <v>0.005253321875346396</v>
+        <v>0.001882914840830655</v>
       </c>
       <c r="D69">
-        <v>0.01845565319095091</v>
+        <v>0.01830515119481938</v>
       </c>
       <c r="E69">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F69">
-        <v>143</v>
+        <v>232</v>
       </c>
       <c r="G69">
-        <v>4.931034482758621</v>
+        <v>4.936170212765957</v>
       </c>
       <c r="H69">
-        <v>0.003427128760572015</v>
+        <v>0.002670080723400003</v>
       </c>
       <c r="I69">
-        <v>0.00671717237072115</v>
+        <v>0.005233358217864006</v>
       </c>
       <c r="J69" t="s">
         <v>30</v>
@@ -3752,28 +3752,28 @@
         <v>9</v>
       </c>
       <c r="B70">
-        <v>-0.1862841657011371</v>
+        <v>-0.1858635037141239</v>
       </c>
       <c r="C70">
-        <v>0.0006496847514437632</v>
+        <v>-0.001324785121833005</v>
       </c>
       <c r="D70">
-        <v>0.01898498665935971</v>
+        <v>0.0176807203608822</v>
       </c>
       <c r="E70">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F70">
-        <v>134</v>
+        <v>222</v>
       </c>
       <c r="G70">
-        <v>4.620689655172414</v>
+        <v>4.723404255319149</v>
       </c>
       <c r="H70">
-        <v>0.00352542351799662</v>
+        <v>0.002578998125116733</v>
       </c>
       <c r="I70">
-        <v>0.006909830095273375</v>
+        <v>0.005054836325228796</v>
       </c>
       <c r="J70" t="s">
         <v>30</v>
@@ -3790,28 +3790,28 @@
         <v>10</v>
       </c>
       <c r="B71">
-        <v>-0.05921039251025104</v>
+        <v>-0.05764459560648255</v>
       </c>
       <c r="C71">
-        <v>-3.752801887013088E-05</v>
+        <v>-0.002503243822072923</v>
       </c>
       <c r="D71">
-        <v>0.01881926415251433</v>
+        <v>0.01791658678155357</v>
       </c>
       <c r="E71">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F71">
-        <v>145</v>
+        <v>235</v>
       </c>
       <c r="G71">
         <v>5</v>
       </c>
       <c r="H71">
-        <v>0.003494649621044418</v>
+        <v>0.002613402778562602</v>
       </c>
       <c r="I71">
-        <v>0.006849513257247059</v>
+        <v>0.0051222694459827</v>
       </c>
       <c r="J71" t="s">
         <v>30</v>
@@ -3828,28 +3828,28 @@
         <v>11</v>
       </c>
       <c r="B72">
-        <v>0.06557938078948672</v>
+        <v>0.06547514583864873</v>
       </c>
       <c r="C72">
-        <v>0.003647235594055888</v>
+        <v>0.004075920294596685</v>
       </c>
       <c r="D72">
-        <v>0.01692105430813966</v>
+        <v>0.01906011265541448</v>
       </c>
       <c r="E72">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F72">
-        <v>131</v>
+        <v>207</v>
       </c>
       <c r="G72">
-        <v>4.517241379310345</v>
+        <v>4.404255319148936</v>
       </c>
       <c r="H72">
-        <v>0.003142160902062255</v>
+        <v>0.002780203170430946</v>
       </c>
       <c r="I72">
-        <v>0.00615863536804202</v>
+        <v>0.005449198214044653</v>
       </c>
       <c r="J72" t="s">
         <v>30</v>
@@ -3866,28 +3866,28 @@
         <v>12</v>
       </c>
       <c r="B73">
-        <v>0.1895324359244286</v>
+        <v>0.1881673433090731</v>
       </c>
       <c r="C73">
-        <v>0.0006828792838841929</v>
+        <v>-0.0007369567877248803</v>
       </c>
       <c r="D73">
-        <v>0.01801500982873545</v>
+        <v>0.01705095577244647</v>
       </c>
       <c r="E73">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F73">
-        <v>141</v>
+        <v>230</v>
       </c>
       <c r="G73">
-        <v>4.862068965517241</v>
+        <v>4.893617021276595</v>
       </c>
       <c r="H73">
-        <v>0.003345303342409943</v>
+        <v>0.00248713751877888</v>
       </c>
       <c r="I73">
-        <v>0.006556794551123488</v>
+        <v>0.004874789536806605</v>
       </c>
       <c r="J73" t="s">
         <v>30</v>
@@ -3904,28 +3904,28 @@
         <v>13</v>
       </c>
       <c r="B74">
-        <v>0.3188384433371824</v>
+        <v>0.3187100001029308</v>
       </c>
       <c r="C74">
-        <v>-0.0001676596313351004</v>
+        <v>0.00451500907260161</v>
       </c>
       <c r="D74">
-        <v>0.01672737152312963</v>
+        <v>0.0151441373822621</v>
       </c>
       <c r="E74">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F74">
-        <v>136</v>
+        <v>224</v>
       </c>
       <c r="G74">
-        <v>4.689655172413793</v>
+        <v>4.76595744680851</v>
       </c>
       <c r="H74">
-        <v>0.003106194911800744</v>
+        <v>0.002208999470506609</v>
       </c>
       <c r="I74">
-        <v>0.006088142027129459</v>
+        <v>0.004329638962192954</v>
       </c>
       <c r="J74" t="s">
         <v>30</v>
@@ -3942,28 +3942,28 @@
         <v>14</v>
       </c>
       <c r="B75">
-        <v>0.4502591638246704</v>
+        <v>0.4506335788764816</v>
       </c>
       <c r="C75">
-        <v>0.005539042905357609</v>
+        <v>0.001282859779093358</v>
       </c>
       <c r="D75">
-        <v>0.01881045363076602</v>
+        <v>0.01660806530438841</v>
       </c>
       <c r="E75">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F75">
-        <v>134</v>
+        <v>216</v>
       </c>
       <c r="G75">
-        <v>4.620689655172414</v>
+        <v>4.595744680851064</v>
       </c>
       <c r="H75">
-        <v>0.003493013548228849</v>
+        <v>0.002422535304421093</v>
       </c>
       <c r="I75">
-        <v>0.006846306554528544</v>
+        <v>0.004748169196665342</v>
       </c>
       <c r="J75" t="s">
         <v>30</v>
@@ -3980,28 +3980,28 @@
         <v>15</v>
       </c>
       <c r="B76">
-        <v>0.5933463431910484</v>
+        <v>0.593429231872045</v>
       </c>
       <c r="C76">
-        <v>0.0001627274966237887</v>
+        <v>0.00214275817272534</v>
       </c>
       <c r="D76">
-        <v>0.02072628665576347</v>
+        <v>0.01889604698465487</v>
       </c>
       <c r="E76">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F76">
-        <v>142</v>
+        <v>231</v>
       </c>
       <c r="G76">
-        <v>4.896551724137931</v>
+        <v>4.914893617021277</v>
       </c>
       <c r="H76">
-        <v>0.003848774809696515</v>
+        <v>0.002756271732760498</v>
       </c>
       <c r="I76">
-        <v>0.007543598627005169</v>
+        <v>0.005402292596210577</v>
       </c>
       <c r="J76" t="s">
         <v>30</v>
@@ -4018,28 +4018,28 @@
         <v>16</v>
       </c>
       <c r="B77">
-        <v>0.7515646096614179</v>
+        <v>0.7505864848301731</v>
       </c>
       <c r="C77">
-        <v>0.0006831932660807842</v>
+        <v>0.008441414126325481</v>
       </c>
       <c r="D77">
-        <v>0.01842923622472659</v>
+        <v>0.02071675500205107</v>
       </c>
       <c r="E77">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F77">
-        <v>137</v>
+        <v>219</v>
       </c>
       <c r="G77">
-        <v>4.724137931034483</v>
+        <v>4.659574468085107</v>
       </c>
       <c r="H77">
-        <v>0.003422223253095378</v>
+        <v>0.003021849292238143</v>
       </c>
       <c r="I77">
-        <v>0.006707557576066941</v>
+        <v>0.005922824612786761</v>
       </c>
       <c r="J77" t="s">
         <v>30</v>
@@ -4056,28 +4056,28 @@
         <v>17</v>
       </c>
       <c r="B78">
-        <v>0.9244632263107666</v>
+        <v>0.9231160573190306</v>
       </c>
       <c r="C78">
-        <v>0.008813439868869351</v>
+        <v>0.003347717860072301</v>
       </c>
       <c r="D78">
-        <v>0.02055561457329419</v>
+        <v>0.01665827896261903</v>
       </c>
       <c r="E78">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F78">
-        <v>132</v>
+        <v>217</v>
       </c>
       <c r="G78">
-        <v>4.551724137931035</v>
+        <v>4.617021276595745</v>
       </c>
       <c r="H78">
-        <v>0.003817081799625</v>
+        <v>0.002429859719251981</v>
       </c>
       <c r="I78">
-        <v>0.007481480327265</v>
+        <v>0.004762525049733882</v>
       </c>
       <c r="J78" t="s">
         <v>30</v>
@@ -4094,28 +4094,28 @@
         <v>18</v>
       </c>
       <c r="B79">
-        <v>1.133010460311121</v>
+        <v>1.133495320936769</v>
       </c>
       <c r="C79">
-        <v>0.0021337824435551</v>
+        <v>0.004795211639425481</v>
       </c>
       <c r="D79">
-        <v>0.01781264611557858</v>
+        <v>0.01979805860361549</v>
       </c>
       <c r="E79">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F79">
-        <v>139</v>
+        <v>227</v>
       </c>
       <c r="G79">
-        <v>4.793103448275862</v>
+        <v>4.829787234042553</v>
       </c>
       <c r="H79">
-        <v>0.003307725344260514</v>
+        <v>0.002887843649891192</v>
       </c>
       <c r="I79">
-        <v>0.006483141674750607</v>
+        <v>0.005660173553786736</v>
       </c>
       <c r="J79" t="s">
         <v>30</v>
@@ -4132,28 +4132,28 @@
         <v>19</v>
       </c>
       <c r="B80">
-        <v>1.424729837353966</v>
+        <v>1.425842255164606</v>
       </c>
       <c r="C80">
-        <v>0.01087878505964208</v>
+        <v>-0.003763483084502355</v>
       </c>
       <c r="D80">
-        <v>0.01841726431047409</v>
+        <v>0.02045076134620701</v>
       </c>
       <c r="E80">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F80">
-        <v>144</v>
+        <v>233</v>
       </c>
       <c r="G80">
-        <v>4.96551724137931</v>
+        <v>4.957446808510638</v>
       </c>
       <c r="H80">
-        <v>0.003420000124429634</v>
+        <v>0.002983050129889957</v>
       </c>
       <c r="I80">
-        <v>0.006703200243882082</v>
+        <v>0.005846778254584315</v>
       </c>
       <c r="J80" t="s">
         <v>30</v>
@@ -4170,28 +4170,28 @@
         <v>20</v>
       </c>
       <c r="B81">
-        <v>2.024128579368942</v>
+        <v>2.0247849307354</v>
       </c>
       <c r="C81">
-        <v>0.006624940217218035</v>
+        <v>0.007538282804669538</v>
       </c>
       <c r="D81">
-        <v>0.01630291280353327</v>
+        <v>0.01801603177981609</v>
       </c>
       <c r="E81">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F81">
-        <v>145</v>
+        <v>235</v>
       </c>
       <c r="G81">
         <v>5</v>
       </c>
       <c r="H81">
-        <v>0.0030273749063231</v>
+        <v>0.002627908322388671</v>
       </c>
       <c r="I81">
-        <v>0.005933654816393276</v>
+        <v>0.005150700311881796</v>
       </c>
       <c r="J81" t="s">
         <v>30</v>
